--- a/rules/CORE-000852/negative/01/data/unit-test-coreid-CG0330-negative.xlsx
+++ b/rules/CORE-000852/negative/01/data/unit-test-coreid-CG0330-negative.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\verisian\core-contributor\rules\CORE-000852\negative\01\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB5F9056-9B41-4D64-91A6-7D41888CB225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B848F65-4212-448F-9DAA-966AF154808A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="858" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30330" yWindow="855" windowWidth="23265" windowHeight="14505" tabRatio="576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="30" r:id="rId1"/>
@@ -20,9 +20,6 @@
     <sheet name="ce.xpt" sheetId="22" r:id="rId5"/>
     <sheet name="lb.xpt" sheetId="23" r:id="rId6"/>
     <sheet name="fa.xpt" sheetId="24" r:id="rId7"/>
-    <sheet name="se.xpt" sheetId="25" r:id="rId8"/>
-    <sheet name="sv.xpt" sheetId="26" r:id="rId9"/>
-    <sheet name="vs.xpt" sheetId="31" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -45,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1046" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="259">
   <si>
     <t>Filename</t>
   </si>
@@ -77,18 +74,6 @@
     <t>Findings About</t>
   </si>
   <si>
-    <t>se.xpt</t>
-  </si>
-  <si>
-    <t>Subject Elements</t>
-  </si>
-  <si>
-    <t>sv.xpt</t>
-  </si>
-  <si>
-    <t>Subject Visits</t>
-  </si>
-  <si>
     <t>Product</t>
   </si>
   <si>
@@ -788,150 +773,6 @@
     <t>LESIONS</t>
   </si>
   <si>
-    <t>SESEQ</t>
-  </si>
-  <si>
-    <t>ETCD</t>
-  </si>
-  <si>
-    <t>ELEMENT</t>
-  </si>
-  <si>
-    <t>SESTDTC</t>
-  </si>
-  <si>
-    <t>SEENDTC</t>
-  </si>
-  <si>
-    <t>SESTDY</t>
-  </si>
-  <si>
-    <t>SEENDY</t>
-  </si>
-  <si>
-    <t>Element Code</t>
-  </si>
-  <si>
-    <t>Description of Element</t>
-  </si>
-  <si>
-    <t>Start Date/Time of Element</t>
-  </si>
-  <si>
-    <t>End Date/Time of Element</t>
-  </si>
-  <si>
-    <t>Study Day of Start of Element</t>
-  </si>
-  <si>
-    <t>Study Day of End of Element</t>
-  </si>
-  <si>
-    <t>SE</t>
-  </si>
-  <si>
-    <t>SCREEN</t>
-  </si>
-  <si>
-    <t>Screening</t>
-  </si>
-  <si>
-    <t>2012-11-23</t>
-  </si>
-  <si>
-    <t>2012-11-30</t>
-  </si>
-  <si>
-    <t>SVDTC</t>
-  </si>
-  <si>
-    <t>SVSTDTC</t>
-  </si>
-  <si>
-    <t>SVENDTC</t>
-  </si>
-  <si>
-    <t>SVSTDY</t>
-  </si>
-  <si>
-    <t>SVENDY</t>
-  </si>
-  <si>
-    <t>SVUPDES</t>
-  </si>
-  <si>
-    <t>Start Date/Time of Visit</t>
-  </si>
-  <si>
-    <t>End Date/Time of Visit</t>
-  </si>
-  <si>
-    <t>Study Day of Start of Visit</t>
-  </si>
-  <si>
-    <t>Study Day of End of Visit</t>
-  </si>
-  <si>
-    <t>Description of Unplanned Visit</t>
-  </si>
-  <si>
-    <t>SV</t>
-  </si>
-  <si>
-    <t>SCREENING 2</t>
-  </si>
-  <si>
-    <t>2012-11-28</t>
-  </si>
-  <si>
-    <t>BASELINE</t>
-  </si>
-  <si>
-    <t>WEEK 2</t>
-  </si>
-  <si>
-    <t>2012-12-13</t>
-  </si>
-  <si>
-    <t>WEEK 4</t>
-  </si>
-  <si>
-    <t>2012-12-26</t>
-  </si>
-  <si>
-    <t>WEEK 4: UNSCHEDULED 01</t>
-  </si>
-  <si>
-    <t>2012-12-28</t>
-  </si>
-  <si>
-    <t>UNSCHEDULED LABS</t>
-  </si>
-  <si>
-    <t>WEEK 6</t>
-  </si>
-  <si>
-    <t>2013-01-10</t>
-  </si>
-  <si>
-    <t>WEEK 8</t>
-  </si>
-  <si>
-    <t>2013-01-23</t>
-  </si>
-  <si>
-    <t>EARLY DISCONTINUATION</t>
-  </si>
-  <si>
-    <t>2013-02-14</t>
-  </si>
-  <si>
-    <t>EARLY DISCONTINUATION RETRIEVAL</t>
-  </si>
-  <si>
-    <t>2013-05-20</t>
-  </si>
-  <si>
     <t>CMDY</t>
   </si>
   <si>
@@ -947,123 +788,9 @@
     <t>LBDY</t>
   </si>
   <si>
-    <t>VSSEQ</t>
-  </si>
-  <si>
-    <t>VSTESTCD</t>
-  </si>
-  <si>
-    <t>VSTEST</t>
-  </si>
-  <si>
-    <t>VSPOS</t>
-  </si>
-  <si>
-    <t>VSORRES</t>
-  </si>
-  <si>
-    <t>VSORRESU</t>
-  </si>
-  <si>
-    <t>VSSTRESC</t>
-  </si>
-  <si>
-    <t>VSSTRESN</t>
-  </si>
-  <si>
-    <t>VSSTRESU</t>
-  </si>
-  <si>
-    <t>VSSTAT</t>
-  </si>
-  <si>
-    <t>VSLOC</t>
-  </si>
-  <si>
-    <t>VSLOBXFL</t>
-  </si>
-  <si>
-    <t>VSREPNUM</t>
-  </si>
-  <si>
-    <t>VSDTC</t>
-  </si>
-  <si>
-    <t>VSDY</t>
-  </si>
-  <si>
-    <t>Vital Signs Test Short Name</t>
-  </si>
-  <si>
-    <t>Vital Signs Test Name</t>
-  </si>
-  <si>
-    <t>Vital Signs Position of Subject</t>
-  </si>
-  <si>
-    <t>Completion Status</t>
-  </si>
-  <si>
-    <t>Location of Vital Signs Measurement</t>
-  </si>
-  <si>
-    <t>Repetition Number</t>
-  </si>
-  <si>
-    <t>Date/Time of Measurements</t>
-  </si>
-  <si>
-    <t>Study Day of Vital Signs</t>
-  </si>
-  <si>
-    <t>VS</t>
-  </si>
-  <si>
-    <t>DIABP</t>
-  </si>
-  <si>
-    <t>Diastolic Blood Pressure</t>
-  </si>
-  <si>
-    <t>STANDING</t>
-  </si>
-  <si>
-    <t>mmHg</t>
-  </si>
-  <si>
-    <t>DIA_BP</t>
-  </si>
-  <si>
-    <t>SUPINE</t>
-  </si>
-  <si>
-    <t>PULSE</t>
-  </si>
-  <si>
-    <t>Pulse Rate</t>
-  </si>
-  <si>
-    <t>beats/min</t>
-  </si>
-  <si>
-    <t>vs.xpt</t>
-  </si>
-  <si>
-    <t>Vital Signs</t>
-  </si>
-  <si>
     <t>CMSTDY</t>
   </si>
   <si>
-    <t>MIDS</t>
-  </si>
-  <si>
-    <t>Disease Milestone Instance Name</t>
-  </si>
-  <si>
-    <t>YES</t>
-  </si>
-  <si>
     <t>Error group</t>
   </si>
   <si>
@@ -1083,13 +810,22 @@
   </si>
   <si>
     <t>Dataset</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>$column_order_from_dataset</t>
+  </si>
+  <si>
+    <t>$column_order_from_library</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1138,21 +874,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1162,18 +885,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor theme="0" tint="-0.14999847407452621"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1248,7 +959,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1271,50 +982,23 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1322,32 +1006,7 @@
     <cellStyle name="Normal 3 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Note" xfId="3" builtinId="10"/>
   </cellStyles>
-  <dxfs count="61">
-    <dxf>
-      <font>
-        <i/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
+  <dxfs count="56">
     <dxf>
       <font>
         <i/>
@@ -1467,100 +1126,6 @@
         </patternFill>
       </fill>
       <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <i/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <i/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFD9D9D9"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9D9D9"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9D9D9"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color rgb="FFD9D9D9"/>
         </left>
@@ -1974,71 +1539,71 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:B8" totalsRowShown="0" headerRowDxfId="60" dataDxfId="59">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:B8" totalsRowShown="0" headerRowDxfId="55" dataDxfId="54">
   <autoFilter ref="A1:B8" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B2">
     <sortCondition ref="A2"/>
   </sortState>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Filename" dataDxfId="58"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Label" dataDxfId="57"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Filename" dataDxfId="53"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Label" dataDxfId="52"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{00000000-000C-0000-FFFF-FFFF0D000000}" name="Table3812" displayName="Table3812" ref="A1:U8" totalsRowShown="0" headerRowDxfId="56" dataDxfId="55">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{00000000-000C-0000-FFFF-FFFF0D000000}" name="Table3812" displayName="Table3812" ref="A1:U8" totalsRowShown="0" headerRowDxfId="51" dataDxfId="50">
   <autoFilter ref="A1:U8" xr:uid="{00000000-0009-0000-0100-00000B000000}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0D00-000001000000}" name="STUDYID" dataDxfId="54"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0D00-000001000000}" name="STUDYID" dataDxfId="49"/>
     <tableColumn id="10" xr3:uid="{96D6F770-5B85-4DEF-80B2-061D4585DD6B}" name="USUBJID"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0D00-000002000000}" name="DOMAIN" dataDxfId="53"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0D00-000004000000}" name="CMSEQ" dataDxfId="52"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0D00-000007000000}" name="CMTRT" dataDxfId="51"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0D00-000010000000}" name="CMINDC" dataDxfId="50"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0D00-000013000000}" name="CMDOSE" dataDxfId="49"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0D00-000015000000}" name="CMDOSU" dataDxfId="48"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0D00-000017000000}" name="CMDOSFRQ" dataDxfId="47"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0D00-00001A000000}" name="CMROUTE" dataDxfId="46"/>
-    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0D00-00001E000000}" name="EPOCH" dataDxfId="45"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0D00-000002000000}" name="DOMAIN" dataDxfId="48"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0D00-000004000000}" name="CMSEQ" dataDxfId="47"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0D00-000007000000}" name="CMTRT" dataDxfId="46"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0D00-000010000000}" name="CMINDC" dataDxfId="45"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0D00-000013000000}" name="CMDOSE" dataDxfId="44"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0D00-000015000000}" name="CMDOSU" dataDxfId="43"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0D00-000017000000}" name="CMDOSFRQ" dataDxfId="42"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0D00-00001A000000}" name="CMROUTE" dataDxfId="41"/>
+    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0D00-00001E000000}" name="EPOCH" dataDxfId="40"/>
     <tableColumn id="8" xr3:uid="{4CAA7607-E56D-4938-A7A9-39467D6C3F14}" name="CMDTC"/>
-    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0D00-00001F000000}" name="CMSTDTC" dataDxfId="44"/>
-    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0D00-000020000000}" name="CMENDTC" dataDxfId="43"/>
+    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0D00-00001F000000}" name="CMSTDTC" dataDxfId="39"/>
+    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0D00-000020000000}" name="CMENDTC" dataDxfId="38"/>
     <tableColumn id="9" xr3:uid="{E1A06B53-CA18-4C63-B5C8-DC4D03B0B4B1}" name="CMDY"/>
-    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0D00-000021000000}" name="CMSTDY" dataDxfId="42"/>
-    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0D00-000022000000}" name="CMENDY" dataDxfId="41"/>
+    <tableColumn id="33" xr3:uid="{00000000-0010-0000-0D00-000021000000}" name="CMSTDY" dataDxfId="37"/>
+    <tableColumn id="34" xr3:uid="{00000000-0010-0000-0D00-000022000000}" name="CMENDY" dataDxfId="36"/>
     <tableColumn id="5" xr3:uid="{9311ED57-1D55-4C10-B428-5D19D65F411D}" name="CMSTRTPT"/>
     <tableColumn id="6" xr3:uid="{3D34C2C3-DFA7-4BFB-A274-E26077754003}" name="CMSTTPT"/>
-    <tableColumn id="40" xr3:uid="{00000000-0010-0000-0D00-000028000000}" name="CMENRTPT" dataDxfId="40"/>
-    <tableColumn id="41" xr3:uid="{00000000-0010-0000-0D00-000029000000}" name="CMENTPT" dataDxfId="39"/>
+    <tableColumn id="40" xr3:uid="{00000000-0010-0000-0D00-000028000000}" name="CMENRTPT" dataDxfId="35"/>
+    <tableColumn id="41" xr3:uid="{00000000-0010-0000-0D00-000029000000}" name="CMENTPT" dataDxfId="34"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{30142334-D948-4D89-9618-60BA25A6797A}" name="Table3811" displayName="Table3811" ref="A1:R18" totalsRowShown="0" headerRowDxfId="38" dataDxfId="37">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{30142334-D948-4D89-9618-60BA25A6797A}" name="Table3811" displayName="Table3811" ref="A1:R18" totalsRowShown="0" headerRowDxfId="33" dataDxfId="32">
   <autoFilter ref="A1:R18" xr:uid="{00000000-0009-0000-0100-00000A000000}"/>
   <tableColumns count="18">
-    <tableColumn id="1" xr3:uid="{04A5A41E-4893-45E2-812B-DC383E1EA614}" name="STUDYID" dataDxfId="36"/>
-    <tableColumn id="2" xr3:uid="{A1DCAC80-9814-41DE-8211-065ADF41AE0B}" name="DOMAIN" dataDxfId="35"/>
-    <tableColumn id="3" xr3:uid="{E3773731-2353-40FA-8499-F547BCACFD09}" name="USUBJID" dataDxfId="34"/>
-    <tableColumn id="4" xr3:uid="{74B4F6B8-3A02-4E04-BAB5-2BD5AC2C243F}" name="CESEQ" dataDxfId="33"/>
-    <tableColumn id="5" xr3:uid="{C6B71A36-69A4-409A-BCE2-A5F6537F2468}" name="CEGRPID" dataDxfId="32"/>
-    <tableColumn id="8" xr3:uid="{9D2DE32A-D92F-43F6-AE20-BD8AD6B3B528}" name="CETERM" dataDxfId="31"/>
-    <tableColumn id="17" xr3:uid="{6773FD6E-49CE-478D-82FB-1EC55CE4F388}" name="CESEV" dataDxfId="30"/>
-    <tableColumn id="20" xr3:uid="{251945F0-E3F1-401F-A7A4-AB5B1A22EE83}" name="EPOCH" dataDxfId="29"/>
-    <tableColumn id="6" xr3:uid="{DA13F58D-F4FA-4D6B-B9EE-7607C2E9E839}" name="CEDTC" dataDxfId="28"/>
-    <tableColumn id="22" xr3:uid="{223AAE33-6248-4CDB-9A67-83A10D29BAC3}" name="CESTDTC" dataDxfId="27"/>
-    <tableColumn id="9" xr3:uid="{CCBF90CB-B344-436B-ABA0-387F99799AF5}" name="CEDY" dataDxfId="26"/>
-    <tableColumn id="23" xr3:uid="{AA7D5334-431F-4E02-B521-3357007B27B2}" name="CEENDTC" dataDxfId="25"/>
-    <tableColumn id="25" xr3:uid="{3E772C43-7996-4B3D-8350-AB90F2239A67}" name="CESTDY" dataDxfId="24"/>
-    <tableColumn id="26" xr3:uid="{D26C22DD-5FE9-4EC4-8682-96A4EB781D6D}" name="CEENDY" dataDxfId="23"/>
-    <tableColumn id="29" xr3:uid="{30EB7BC8-CE60-4A2A-A7D0-1B0B0AA50088}" name="CESTRTPT" dataDxfId="22"/>
-    <tableColumn id="30" xr3:uid="{C66BBA71-6BF4-4CC5-ADF2-7028B52970D4}" name="CESTTPT" dataDxfId="21"/>
-    <tableColumn id="31" xr3:uid="{38C1A2B8-1D39-4D6E-8220-A650CEDD7F80}" name="CEENRTPT" dataDxfId="20"/>
-    <tableColumn id="32" xr3:uid="{372C7AB9-9C2E-4CFC-BD3D-F9CA28FCE23F}" name="CEENTPT" dataDxfId="19"/>
+    <tableColumn id="1" xr3:uid="{04A5A41E-4893-45E2-812B-DC383E1EA614}" name="STUDYID" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{A1DCAC80-9814-41DE-8211-065ADF41AE0B}" name="DOMAIN" dataDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{E3773731-2353-40FA-8499-F547BCACFD09}" name="USUBJID" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{74B4F6B8-3A02-4E04-BAB5-2BD5AC2C243F}" name="CESEQ" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{C6B71A36-69A4-409A-BCE2-A5F6537F2468}" name="CEGRPID" dataDxfId="27"/>
+    <tableColumn id="8" xr3:uid="{9D2DE32A-D92F-43F6-AE20-BD8AD6B3B528}" name="CETERM" dataDxfId="26"/>
+    <tableColumn id="17" xr3:uid="{6773FD6E-49CE-478D-82FB-1EC55CE4F388}" name="CESEV" dataDxfId="25"/>
+    <tableColumn id="20" xr3:uid="{251945F0-E3F1-401F-A7A4-AB5B1A22EE83}" name="EPOCH" dataDxfId="24"/>
+    <tableColumn id="6" xr3:uid="{DA13F58D-F4FA-4D6B-B9EE-7607C2E9E839}" name="CEDTC" dataDxfId="23"/>
+    <tableColumn id="22" xr3:uid="{223AAE33-6248-4CDB-9A67-83A10D29BAC3}" name="CESTDTC" dataDxfId="22"/>
+    <tableColumn id="9" xr3:uid="{CCBF90CB-B344-436B-ABA0-387F99799AF5}" name="CEDY" dataDxfId="21"/>
+    <tableColumn id="23" xr3:uid="{AA7D5334-431F-4E02-B521-3357007B27B2}" name="CEENDTC" dataDxfId="20"/>
+    <tableColumn id="25" xr3:uid="{3E772C43-7996-4B3D-8350-AB90F2239A67}" name="CESTDY" dataDxfId="19"/>
+    <tableColumn id="26" xr3:uid="{D26C22DD-5FE9-4EC4-8682-96A4EB781D6D}" name="CEENDY" dataDxfId="18"/>
+    <tableColumn id="29" xr3:uid="{30EB7BC8-CE60-4A2A-A7D0-1B0B0AA50088}" name="CESTRTPT" dataDxfId="17"/>
+    <tableColumn id="30" xr3:uid="{C66BBA71-6BF4-4CC5-ADF2-7028B52970D4}" name="CESTTPT" dataDxfId="16"/>
+    <tableColumn id="31" xr3:uid="{38C1A2B8-1D39-4D6E-8220-A650CEDD7F80}" name="CEENRTPT" dataDxfId="15"/>
+    <tableColumn id="32" xr3:uid="{372C7AB9-9C2E-4CFC-BD3D-F9CA28FCE23F}" name="CEENTPT" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2068,9 +1633,9 @@
     <tableColumn id="18" xr3:uid="{FA0266C4-48EF-414C-A944-5AA76B17A0E1}" name="LBLOBXFL"/>
     <tableColumn id="19" xr3:uid="{0D5094A9-7A7A-42F7-ABE4-F131723B5686}" name="VISITNUM"/>
     <tableColumn id="20" xr3:uid="{0796BA4F-27CA-41AE-9446-B3A986D0EED1}" name="VISIT"/>
-    <tableColumn id="21" xr3:uid="{B02D8050-8C66-44C0-A7E5-F614C9F283BA}" name="LBDY" dataDxfId="18"/>
-    <tableColumn id="26" xr3:uid="{B8E04BE0-945B-462B-88F9-FB08FFF188A2}" name="LBENRTPT" dataDxfId="17"/>
-    <tableColumn id="25" xr3:uid="{0016D6C5-5528-4EEA-8A08-70C59CC58DFC}" name="LBENTPT" dataDxfId="16"/>
+    <tableColumn id="21" xr3:uid="{B02D8050-8C66-44C0-A7E5-F614C9F283BA}" name="LBDY" dataDxfId="13"/>
+    <tableColumn id="26" xr3:uid="{B8E04BE0-945B-462B-88F9-FB08FFF188A2}" name="LBENRTPT" dataDxfId="12"/>
+    <tableColumn id="25" xr3:uid="{0016D6C5-5528-4EEA-8A08-70C59CC58DFC}" name="LBENTPT" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2088,37 +1653,17 @@
     <tableColumn id="6" xr3:uid="{4DE05E4E-B951-443D-B31D-CFAD28125FB4}" name="FATESTCD"/>
     <tableColumn id="7" xr3:uid="{2D1EC35B-0AD5-4D6D-A925-CA5F001333D0}" name="FATEST"/>
     <tableColumn id="8" xr3:uid="{CA5ADBF8-3392-4070-9FB0-8814222755E2}" name="FAOBJ"/>
-    <tableColumn id="19" xr3:uid="{35871A4F-DB35-4344-8F65-55991861F7C8}" name="FASTRESC" dataDxfId="15"/>
+    <tableColumn id="19" xr3:uid="{35871A4F-DB35-4344-8F65-55991861F7C8}" name="FASTRESC" dataDxfId="10"/>
     <tableColumn id="10" xr3:uid="{C94B98A5-DC3D-401D-B024-5B01B3AE31BD}" name="FAORRES"/>
-    <tableColumn id="18" xr3:uid="{68E3FDB0-9ACE-4307-AF1A-1EF294A87018}" name="FASTNRLO" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{CE72CD1A-F312-4BB3-9890-2151C25B1631}" name="FASTNRHI" dataDxfId="13"/>
+    <tableColumn id="18" xr3:uid="{68E3FDB0-9ACE-4307-AF1A-1EF294A87018}" name="FASTNRLO" dataDxfId="9"/>
+    <tableColumn id="9" xr3:uid="{CE72CD1A-F312-4BB3-9890-2151C25B1631}" name="FASTNRHI" dataDxfId="8"/>
     <tableColumn id="12" xr3:uid="{50829580-2CC5-46DA-9800-13342647E277}" name="FALOC"/>
     <tableColumn id="13" xr3:uid="{721BDBFE-9FA6-4B5D-B524-A621E577525B}" name="VISITNUM"/>
     <tableColumn id="14" xr3:uid="{646B92E3-685D-43BF-A3BD-493B6F611ADC}" name="EPOCH"/>
     <tableColumn id="15" xr3:uid="{7049E1FA-7BE1-4EED-BA07-BC48B0A38833}" name="FADTC"/>
-    <tableColumn id="11" xr3:uid="{33CB4431-7585-4196-8760-5633C81932FA}" name="FADY" dataDxfId="12"/>
-    <tableColumn id="20" xr3:uid="{CB971A8F-2BE4-42D5-B8DE-BCA415C25ADA}" name="FAENRTPT" dataDxfId="11"/>
-    <tableColumn id="17" xr3:uid="{83400486-E83B-4077-95BF-86826F0864AA}" name="FAENTPT" dataDxfId="10"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{A207061D-835A-4982-BF04-E54C33C8229E}" name="Table16" displayName="Table16" ref="A1:K14" totalsRowShown="0">
-  <autoFilter ref="A1:K14" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{1D58E98C-B945-4C87-8E2A-0FEA73AE549D}" name="STUDYID"/>
-    <tableColumn id="2" xr3:uid="{1D0855B8-630C-4D6C-8431-C892539C3FEE}" name="DOMAIN"/>
-    <tableColumn id="3" xr3:uid="{EB4DC0E9-74D0-45B0-B48C-976415926D48}" name="USUBJID"/>
-    <tableColumn id="4" xr3:uid="{1D20E663-979E-4E98-8462-9AF713517179}" name="VISITNUM"/>
-    <tableColumn id="5" xr3:uid="{382E5FB6-F44B-490E-9F94-8FF782791E3A}" name="VISIT" dataDxfId="9"/>
-    <tableColumn id="14" xr3:uid="{E25C625D-7D53-4BC7-97BE-8646159227C2}" name="SVDTC" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{BAA90379-2A20-4B97-B12D-0330215DFAA5}" name="SVSTDTC"/>
-    <tableColumn id="7" xr3:uid="{6066B00F-AEB1-4C32-8832-8F31CA11CFCF}" name="SVENDTC"/>
-    <tableColumn id="8" xr3:uid="{C004D32F-83FD-4CB7-9616-1388F849ABC9}" name="SVSTDY"/>
-    <tableColumn id="9" xr3:uid="{63383886-BB7D-4F54-B69B-13B14C828753}" name="SVENDY"/>
-    <tableColumn id="10" xr3:uid="{8BCA649E-FCE6-4B24-972D-462D7D911C58}" name="SVUPDES"/>
+    <tableColumn id="11" xr3:uid="{33CB4431-7585-4196-8760-5633C81932FA}" name="FADY" dataDxfId="7"/>
+    <tableColumn id="20" xr3:uid="{CB971A8F-2BE4-42D5-B8DE-BCA415C25ADA}" name="FAENRTPT" dataDxfId="6"/>
+    <tableColumn id="17" xr3:uid="{83400486-E83B-4077-95BF-86826F0864AA}" name="FAENTPT" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2392,1476 +1937,28 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>17</v>
+        <v>12</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B645C89-E05F-455F-8D1D-76D1DA1878BA}">
-  <dimension ref="A1:V23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="5" max="5" width="19" customWidth="1"/>
-    <col min="7" max="8" width="12.42578125" customWidth="1"/>
-    <col min="10" max="10" width="13.140625" customWidth="1"/>
-    <col min="11" max="11" width="12.85546875" customWidth="1"/>
-    <col min="12" max="12" width="13.85546875" customWidth="1"/>
-    <col min="13" max="13" width="13" customWidth="1"/>
-    <col min="16" max="16" width="13.85546875" customWidth="1"/>
-    <col min="17" max="17" width="13.42578125" customWidth="1"/>
-    <col min="18" max="18" width="12.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C1" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="D1" s="16" t="s">
-        <v>300</v>
-      </c>
-      <c r="E1" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="F1" s="16" t="s">
-        <v>302</v>
-      </c>
-      <c r="G1" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="H1" s="22" t="s">
-        <v>336</v>
-      </c>
-      <c r="I1" s="16" t="s">
-        <v>304</v>
-      </c>
-      <c r="J1" s="16" t="s">
-        <v>305</v>
-      </c>
-      <c r="K1" s="16" t="s">
-        <v>306</v>
-      </c>
-      <c r="L1" s="16" t="s">
-        <v>307</v>
-      </c>
-      <c r="M1" s="16" t="s">
-        <v>308</v>
-      </c>
-      <c r="N1" s="16" t="s">
-        <v>309</v>
-      </c>
-      <c r="O1" s="16" t="s">
-        <v>310</v>
-      </c>
-      <c r="P1" s="16" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q1" s="16" t="s">
-        <v>312</v>
-      </c>
-      <c r="R1" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="S1" s="16" t="s">
-        <v>161</v>
-      </c>
-      <c r="T1" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="U1" s="16" t="s">
-        <v>313</v>
-      </c>
-      <c r="V1" s="16" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22" ht="75" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="C2" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="D2" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>315</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>316</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>317</v>
-      </c>
-      <c r="H2" s="17" t="s">
-        <v>337</v>
-      </c>
-      <c r="I2" s="17" t="s">
-        <v>168</v>
-      </c>
-      <c r="J2" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="K2" s="17" t="s">
-        <v>172</v>
-      </c>
-      <c r="L2" s="17" t="s">
-        <v>173</v>
-      </c>
-      <c r="M2" s="17" t="s">
-        <v>174</v>
-      </c>
-      <c r="N2" s="17" t="s">
-        <v>318</v>
-      </c>
-      <c r="O2" s="17" t="s">
-        <v>319</v>
-      </c>
-      <c r="P2" s="17" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q2" s="17" t="s">
-        <v>320</v>
-      </c>
-      <c r="R2" s="17" t="s">
-        <v>179</v>
-      </c>
-      <c r="S2" s="17" t="s">
-        <v>180</v>
-      </c>
-      <c r="T2" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="U2" s="17" t="s">
-        <v>321</v>
-      </c>
-      <c r="V2" s="17" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="E3" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="F3" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="G3" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="H3" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="I3" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="J3" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="K3" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="L3" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="M3" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="N3" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="O3" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="P3" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q3" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="R3" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="S3" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="T3" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="U3" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="V3" s="18" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A4" s="17">
-        <v>12</v>
-      </c>
-      <c r="B4" s="17">
-        <v>2</v>
-      </c>
-      <c r="C4" s="17">
-        <v>8</v>
-      </c>
-      <c r="D4" s="17">
-        <v>8</v>
-      </c>
-      <c r="E4" s="19">
-        <v>8</v>
-      </c>
-      <c r="F4" s="17">
-        <v>24</v>
-      </c>
-      <c r="G4" s="17">
-        <v>8</v>
-      </c>
-      <c r="H4" s="17">
-        <v>8</v>
-      </c>
-      <c r="I4" s="17">
-        <v>8</v>
-      </c>
-      <c r="J4" s="17">
-        <v>9</v>
-      </c>
-      <c r="K4" s="17">
-        <v>200</v>
-      </c>
-      <c r="L4" s="17">
-        <v>8</v>
-      </c>
-      <c r="M4" s="17">
-        <v>9</v>
-      </c>
-      <c r="N4" s="17">
-        <v>8</v>
-      </c>
-      <c r="O4" s="17">
-        <v>11</v>
-      </c>
-      <c r="P4" s="17">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="17">
-        <v>8</v>
-      </c>
-      <c r="R4" s="17">
-        <v>8</v>
-      </c>
-      <c r="S4" s="17">
-        <v>200</v>
-      </c>
-      <c r="T4" s="17">
-        <v>9</v>
-      </c>
-      <c r="U4" s="17">
-        <v>10</v>
-      </c>
-      <c r="V4" s="17">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>323</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="D5" s="18">
-        <v>1</v>
-      </c>
-      <c r="E5" s="18" t="s">
-        <v>324</v>
-      </c>
-      <c r="F5" s="18" t="s">
-        <v>325</v>
-      </c>
-      <c r="G5" s="18" t="s">
-        <v>326</v>
-      </c>
-      <c r="H5" s="18" t="s">
-        <v>338</v>
-      </c>
-      <c r="I5" s="20">
-        <v>71</v>
-      </c>
-      <c r="J5" s="18" t="s">
-        <v>327</v>
-      </c>
-      <c r="K5" s="20">
-        <v>71</v>
-      </c>
-      <c r="L5" s="18">
-        <v>71</v>
-      </c>
-      <c r="M5" s="18" t="s">
-        <v>327</v>
-      </c>
-      <c r="N5" s="18"/>
-      <c r="O5" s="18"/>
-      <c r="P5" s="18"/>
-      <c r="Q5" s="18"/>
-      <c r="R5" s="18">
-        <v>1</v>
-      </c>
-      <c r="S5" s="18" t="s">
-        <v>194</v>
-      </c>
-      <c r="T5" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="U5" s="18" t="s">
-        <v>263</v>
-      </c>
-      <c r="V5" s="18">
-        <v>-7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>323</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="D6" s="17">
-        <v>2</v>
-      </c>
-      <c r="E6" s="17" t="s">
-        <v>324</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>325</v>
-      </c>
-      <c r="G6" s="17" t="s">
-        <v>326</v>
-      </c>
-      <c r="H6" s="18" t="s">
-        <v>338</v>
-      </c>
-      <c r="I6" s="19">
-        <v>71</v>
-      </c>
-      <c r="J6" s="17" t="s">
-        <v>327</v>
-      </c>
-      <c r="K6" s="19">
-        <v>71</v>
-      </c>
-      <c r="L6" s="17">
-        <v>71</v>
-      </c>
-      <c r="M6" s="17" t="s">
-        <v>327</v>
-      </c>
-      <c r="N6" s="17"/>
-      <c r="O6" s="17"/>
-      <c r="P6" s="17"/>
-      <c r="Q6" s="17"/>
-      <c r="R6" s="17">
-        <v>2</v>
-      </c>
-      <c r="S6" s="17" t="s">
-        <v>277</v>
-      </c>
-      <c r="T6" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="U6" s="17" t="s">
-        <v>278</v>
-      </c>
-      <c r="V6" s="17">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" ht="45" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>323</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="D7" s="18">
-        <v>3</v>
-      </c>
-      <c r="E7" s="18" t="s">
-        <v>324</v>
-      </c>
-      <c r="F7" s="18" t="s">
-        <v>325</v>
-      </c>
-      <c r="G7" s="18" t="s">
-        <v>326</v>
-      </c>
-      <c r="H7" s="18" t="s">
-        <v>338</v>
-      </c>
-      <c r="I7" s="20">
-        <v>83</v>
-      </c>
-      <c r="J7" s="18" t="s">
-        <v>327</v>
-      </c>
-      <c r="K7" s="20">
-        <v>83</v>
-      </c>
-      <c r="L7" s="18">
-        <v>83</v>
-      </c>
-      <c r="M7" s="18" t="s">
-        <v>327</v>
-      </c>
-      <c r="N7" s="18"/>
-      <c r="O7" s="18"/>
-      <c r="P7" s="18" t="s">
-        <v>193</v>
-      </c>
-      <c r="Q7" s="18"/>
-      <c r="R7" s="18">
-        <v>3</v>
-      </c>
-      <c r="S7" s="18" t="s">
-        <v>279</v>
-      </c>
-      <c r="T7" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="U7" s="18" t="s">
-        <v>264</v>
-      </c>
-      <c r="V7" s="18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" ht="45" x14ac:dyDescent="0.25">
-      <c r="A8" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>323</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="D8" s="17">
-        <v>4</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>324</v>
-      </c>
-      <c r="F8" s="17" t="s">
-        <v>325</v>
-      </c>
-      <c r="G8" s="17" t="s">
-        <v>326</v>
-      </c>
-      <c r="H8" s="18" t="s">
-        <v>338</v>
-      </c>
-      <c r="I8" s="19">
-        <v>79</v>
-      </c>
-      <c r="J8" s="17" t="s">
-        <v>327</v>
-      </c>
-      <c r="K8" s="19">
-        <v>79</v>
-      </c>
-      <c r="L8" s="17">
-        <v>79</v>
-      </c>
-      <c r="M8" s="17" t="s">
-        <v>327</v>
-      </c>
-      <c r="N8" s="17"/>
-      <c r="O8" s="17"/>
-      <c r="P8" s="17"/>
-      <c r="Q8" s="17"/>
-      <c r="R8" s="17">
-        <v>4</v>
-      </c>
-      <c r="S8" s="17" t="s">
-        <v>280</v>
-      </c>
-      <c r="T8" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="U8" s="17" t="s">
-        <v>281</v>
-      </c>
-      <c r="V8" s="17">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>323</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="D9" s="18">
-        <v>5</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>324</v>
-      </c>
-      <c r="F9" s="18" t="s">
-        <v>325</v>
-      </c>
-      <c r="G9" s="18" t="s">
-        <v>326</v>
-      </c>
-      <c r="H9" s="18" t="s">
-        <v>338</v>
-      </c>
-      <c r="I9" s="20">
-        <v>68</v>
-      </c>
-      <c r="J9" s="18" t="s">
-        <v>327</v>
-      </c>
-      <c r="K9" s="20">
-        <v>68</v>
-      </c>
-      <c r="L9" s="18">
-        <v>68</v>
-      </c>
-      <c r="M9" s="18" t="s">
-        <v>327</v>
-      </c>
-      <c r="N9" s="18"/>
-      <c r="O9" s="18"/>
-      <c r="P9" s="18"/>
-      <c r="Q9" s="18"/>
-      <c r="R9" s="18">
-        <v>5</v>
-      </c>
-      <c r="S9" s="18" t="s">
-        <v>282</v>
-      </c>
-      <c r="T9" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="U9" s="18" t="s">
-        <v>283</v>
-      </c>
-      <c r="V9" s="18">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" ht="45" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>323</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="D10" s="17">
-        <v>6</v>
-      </c>
-      <c r="E10" s="17" t="s">
-        <v>328</v>
-      </c>
-      <c r="F10" s="17" t="s">
-        <v>325</v>
-      </c>
-      <c r="G10" s="17" t="s">
-        <v>329</v>
-      </c>
-      <c r="H10" s="18" t="s">
-        <v>338</v>
-      </c>
-      <c r="I10" s="19">
-        <v>77</v>
-      </c>
-      <c r="J10" s="17" t="s">
-        <v>327</v>
-      </c>
-      <c r="K10" s="19">
-        <v>77</v>
-      </c>
-      <c r="L10" s="17">
-        <v>77</v>
-      </c>
-      <c r="M10" s="17" t="s">
-        <v>327</v>
-      </c>
-      <c r="N10" s="17"/>
-      <c r="O10" s="17"/>
-      <c r="P10" s="17"/>
-      <c r="Q10" s="17">
-        <v>1</v>
-      </c>
-      <c r="R10" s="17">
-        <v>7</v>
-      </c>
-      <c r="S10" s="17" t="s">
-        <v>287</v>
-      </c>
-      <c r="T10" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="U10" s="17" t="s">
-        <v>288</v>
-      </c>
-      <c r="V10" s="17">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>323</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="D11" s="18">
-        <v>7</v>
-      </c>
-      <c r="E11" s="18" t="s">
-        <v>324</v>
-      </c>
-      <c r="F11" s="18" t="s">
-        <v>325</v>
-      </c>
-      <c r="G11" s="18" t="s">
-        <v>326</v>
-      </c>
-      <c r="H11" s="18" t="s">
-        <v>338</v>
-      </c>
-      <c r="I11" s="20">
-        <v>71</v>
-      </c>
-      <c r="J11" s="18" t="s">
-        <v>327</v>
-      </c>
-      <c r="K11" s="20">
-        <v>71</v>
-      </c>
-      <c r="L11" s="18">
-        <v>71</v>
-      </c>
-      <c r="M11" s="18" t="s">
-        <v>327</v>
-      </c>
-      <c r="N11" s="18"/>
-      <c r="O11" s="18"/>
-      <c r="P11" s="18"/>
-      <c r="Q11" s="18">
-        <v>2</v>
-      </c>
-      <c r="R11" s="18">
-        <v>7</v>
-      </c>
-      <c r="S11" s="18" t="s">
-        <v>287</v>
-      </c>
-      <c r="T11" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="U11" s="18" t="s">
-        <v>288</v>
-      </c>
-      <c r="V11" s="18">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" ht="45" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>323</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="D12" s="17">
-        <v>8</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>324</v>
-      </c>
-      <c r="F12" s="17" t="s">
-        <v>325</v>
-      </c>
-      <c r="G12" s="17" t="s">
-        <v>326</v>
-      </c>
-      <c r="H12" s="18" t="s">
-        <v>338</v>
-      </c>
-      <c r="I12" s="19">
-        <v>69</v>
-      </c>
-      <c r="J12" s="17" t="s">
-        <v>327</v>
-      </c>
-      <c r="K12" s="19">
-        <v>69</v>
-      </c>
-      <c r="L12" s="17">
-        <v>69</v>
-      </c>
-      <c r="M12" s="17" t="s">
-        <v>327</v>
-      </c>
-      <c r="N12" s="17"/>
-      <c r="O12" s="17"/>
-      <c r="P12" s="17"/>
-      <c r="Q12" s="17">
-        <v>3</v>
-      </c>
-      <c r="R12" s="17">
-        <v>7</v>
-      </c>
-      <c r="S12" s="17" t="s">
-        <v>287</v>
-      </c>
-      <c r="T12" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="U12" s="17" t="s">
-        <v>288</v>
-      </c>
-      <c r="V12" s="17">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" ht="45" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>323</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="D13" s="18">
-        <v>9</v>
-      </c>
-      <c r="E13" s="18" t="s">
-        <v>324</v>
-      </c>
-      <c r="F13" s="18" t="s">
-        <v>325</v>
-      </c>
-      <c r="G13" s="18" t="s">
-        <v>329</v>
-      </c>
-      <c r="H13" s="18" t="s">
-        <v>338</v>
-      </c>
-      <c r="I13" s="20">
-        <v>76</v>
-      </c>
-      <c r="J13" s="18" t="s">
-        <v>327</v>
-      </c>
-      <c r="K13" s="20">
-        <v>76</v>
-      </c>
-      <c r="L13" s="18">
-        <v>76</v>
-      </c>
-      <c r="M13" s="18" t="s">
-        <v>327</v>
-      </c>
-      <c r="N13" s="18"/>
-      <c r="O13" s="18"/>
-      <c r="P13" s="18"/>
-      <c r="Q13" s="18">
-        <v>1</v>
-      </c>
-      <c r="R13" s="18">
-        <v>8</v>
-      </c>
-      <c r="S13" s="18" t="s">
-        <v>289</v>
-      </c>
-      <c r="T13" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="U13" s="18" t="s">
-        <v>290</v>
-      </c>
-      <c r="V13" s="18">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="B14" s="17" t="s">
-        <v>323</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="D14" s="17">
-        <v>20</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>330</v>
-      </c>
-      <c r="F14" s="17" t="s">
-        <v>331</v>
-      </c>
-      <c r="G14" s="17" t="s">
-        <v>326</v>
-      </c>
-      <c r="H14" s="18" t="s">
-        <v>338</v>
-      </c>
-      <c r="I14" s="19">
-        <v>51</v>
-      </c>
-      <c r="J14" s="17" t="s">
-        <v>332</v>
-      </c>
-      <c r="K14" s="19">
-        <v>51</v>
-      </c>
-      <c r="L14" s="17">
-        <v>51</v>
-      </c>
-      <c r="M14" s="17" t="s">
-        <v>332</v>
-      </c>
-      <c r="N14" s="17"/>
-      <c r="O14" s="17"/>
-      <c r="P14" s="17"/>
-      <c r="Q14" s="17"/>
-      <c r="R14" s="17">
-        <v>5</v>
-      </c>
-      <c r="S14" s="17" t="s">
-        <v>282</v>
-      </c>
-      <c r="T14" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="U14" s="17" t="s">
-        <v>283</v>
-      </c>
-      <c r="V14" s="17">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="B15" s="18" t="s">
-        <v>323</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="D15" s="18">
-        <v>21</v>
-      </c>
-      <c r="E15" s="18" t="s">
-        <v>330</v>
-      </c>
-      <c r="F15" s="18" t="s">
-        <v>331</v>
-      </c>
-      <c r="G15" s="18" t="s">
-        <v>329</v>
-      </c>
-      <c r="H15" s="18"/>
-      <c r="I15" s="20">
-        <v>52</v>
-      </c>
-      <c r="J15" s="18" t="s">
-        <v>332</v>
-      </c>
-      <c r="K15" s="20">
-        <v>52</v>
-      </c>
-      <c r="L15" s="18">
-        <v>52</v>
-      </c>
-      <c r="M15" s="18" t="s">
-        <v>332</v>
-      </c>
-      <c r="N15" s="18"/>
-      <c r="O15" s="18"/>
-      <c r="P15" s="18"/>
-      <c r="Q15" s="18">
-        <v>1</v>
-      </c>
-      <c r="R15" s="18">
-        <v>7</v>
-      </c>
-      <c r="S15" s="18" t="s">
-        <v>287</v>
-      </c>
-      <c r="T15" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="U15" s="18" t="s">
-        <v>288</v>
-      </c>
-      <c r="V15" s="18">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="B16" s="17" t="s">
-        <v>323</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="D16" s="17">
-        <v>22</v>
-      </c>
-      <c r="E16" s="17" t="s">
-        <v>330</v>
-      </c>
-      <c r="F16" s="17" t="s">
-        <v>331</v>
-      </c>
-      <c r="G16" s="17" t="s">
-        <v>326</v>
-      </c>
-      <c r="H16" s="17"/>
-      <c r="I16" s="19">
-        <v>62</v>
-      </c>
-      <c r="J16" s="17" t="s">
-        <v>332</v>
-      </c>
-      <c r="K16" s="19">
-        <v>62</v>
-      </c>
-      <c r="L16" s="17">
-        <v>62</v>
-      </c>
-      <c r="M16" s="17" t="s">
-        <v>332</v>
-      </c>
-      <c r="N16" s="17"/>
-      <c r="O16" s="17"/>
-      <c r="P16" s="17"/>
-      <c r="Q16" s="17">
-        <v>2</v>
-      </c>
-      <c r="R16" s="17">
-        <v>7</v>
-      </c>
-      <c r="S16" s="17" t="s">
-        <v>287</v>
-      </c>
-      <c r="T16" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="U16" s="17" t="s">
-        <v>288</v>
-      </c>
-      <c r="V16" s="17">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="B17" s="18" t="s">
-        <v>323</v>
-      </c>
-      <c r="C17" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="D17" s="18">
-        <v>23</v>
-      </c>
-      <c r="E17" s="18" t="s">
-        <v>330</v>
-      </c>
-      <c r="F17" s="18" t="s">
-        <v>331</v>
-      </c>
-      <c r="G17" s="18" t="s">
-        <v>326</v>
-      </c>
-      <c r="H17" s="18"/>
-      <c r="I17" s="20">
-        <v>62</v>
-      </c>
-      <c r="J17" s="18" t="s">
-        <v>332</v>
-      </c>
-      <c r="K17" s="20">
-        <v>62</v>
-      </c>
-      <c r="L17" s="18">
-        <v>62</v>
-      </c>
-      <c r="M17" s="18" t="s">
-        <v>332</v>
-      </c>
-      <c r="N17" s="18"/>
-      <c r="O17" s="18"/>
-      <c r="P17" s="18"/>
-      <c r="Q17" s="18">
-        <v>3</v>
-      </c>
-      <c r="R17" s="18">
-        <v>7</v>
-      </c>
-      <c r="S17" s="18" t="s">
-        <v>287</v>
-      </c>
-      <c r="T17" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="U17" s="18" t="s">
-        <v>288</v>
-      </c>
-      <c r="V17" s="18">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="B18" s="17" t="s">
-        <v>323</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="D18" s="17">
-        <v>24</v>
-      </c>
-      <c r="E18" s="17" t="s">
-        <v>330</v>
-      </c>
-      <c r="F18" s="17" t="s">
-        <v>331</v>
-      </c>
-      <c r="G18" s="17" t="s">
-        <v>329</v>
-      </c>
-      <c r="H18" s="17"/>
-      <c r="I18" s="19">
-        <v>50</v>
-      </c>
-      <c r="J18" s="17" t="s">
-        <v>332</v>
-      </c>
-      <c r="K18" s="19">
-        <v>50</v>
-      </c>
-      <c r="L18" s="17">
-        <v>50</v>
-      </c>
-      <c r="M18" s="17" t="s">
-        <v>332</v>
-      </c>
-      <c r="N18" s="17"/>
-      <c r="O18" s="17"/>
-      <c r="P18" s="17"/>
-      <c r="Q18" s="17">
-        <v>1</v>
-      </c>
-      <c r="R18" s="17">
-        <v>8</v>
-      </c>
-      <c r="S18" s="17" t="s">
-        <v>289</v>
-      </c>
-      <c r="T18" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="U18" s="17" t="s">
-        <v>290</v>
-      </c>
-      <c r="V18" s="17">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="B19" s="18" t="s">
-        <v>323</v>
-      </c>
-      <c r="C19" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="D19" s="18">
-        <v>25</v>
-      </c>
-      <c r="E19" s="18" t="s">
-        <v>330</v>
-      </c>
-      <c r="F19" s="18" t="s">
-        <v>331</v>
-      </c>
-      <c r="G19" s="18" t="s">
-        <v>326</v>
-      </c>
-      <c r="H19" s="18"/>
-      <c r="I19" s="20">
-        <v>52</v>
-      </c>
-      <c r="J19" s="18" t="s">
-        <v>332</v>
-      </c>
-      <c r="K19" s="20">
-        <v>52</v>
-      </c>
-      <c r="L19" s="18">
-        <v>52</v>
-      </c>
-      <c r="M19" s="18" t="s">
-        <v>332</v>
-      </c>
-      <c r="N19" s="18"/>
-      <c r="O19" s="18"/>
-      <c r="P19" s="18"/>
-      <c r="Q19" s="18">
-        <v>2</v>
-      </c>
-      <c r="R19" s="18">
-        <v>8</v>
-      </c>
-      <c r="S19" s="18" t="s">
-        <v>289</v>
-      </c>
-      <c r="T19" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="U19" s="18" t="s">
-        <v>290</v>
-      </c>
-      <c r="V19" s="18">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="B20" s="17" t="s">
-        <v>323</v>
-      </c>
-      <c r="C20" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="D20" s="17">
-        <v>26</v>
-      </c>
-      <c r="E20" s="17" t="s">
-        <v>330</v>
-      </c>
-      <c r="F20" s="17" t="s">
-        <v>331</v>
-      </c>
-      <c r="G20" s="17" t="s">
-        <v>326</v>
-      </c>
-      <c r="H20" s="17"/>
-      <c r="I20" s="19">
-        <v>54</v>
-      </c>
-      <c r="J20" s="17" t="s">
-        <v>332</v>
-      </c>
-      <c r="K20" s="19">
-        <v>54</v>
-      </c>
-      <c r="L20" s="17">
-        <v>54</v>
-      </c>
-      <c r="M20" s="17" t="s">
-        <v>332</v>
-      </c>
-      <c r="N20" s="17"/>
-      <c r="O20" s="17"/>
-      <c r="P20" s="17"/>
-      <c r="Q20" s="17">
-        <v>3</v>
-      </c>
-      <c r="R20" s="17">
-        <v>8</v>
-      </c>
-      <c r="S20" s="17" t="s">
-        <v>289</v>
-      </c>
-      <c r="T20" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="U20" s="17" t="s">
-        <v>290</v>
-      </c>
-      <c r="V20" s="17">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22" ht="90" x14ac:dyDescent="0.25">
-      <c r="A21" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="B21" s="18" t="s">
-        <v>323</v>
-      </c>
-      <c r="C21" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="D21" s="18">
-        <v>27</v>
-      </c>
-      <c r="E21" s="18" t="s">
-        <v>330</v>
-      </c>
-      <c r="F21" s="18" t="s">
-        <v>331</v>
-      </c>
-      <c r="G21" s="18" t="s">
-        <v>329</v>
-      </c>
-      <c r="H21" s="18"/>
-      <c r="I21" s="20">
-        <v>79</v>
-      </c>
-      <c r="J21" s="18" t="s">
-        <v>332</v>
-      </c>
-      <c r="K21" s="20">
-        <v>79</v>
-      </c>
-      <c r="L21" s="18">
-        <v>79</v>
-      </c>
-      <c r="M21" s="18" t="s">
-        <v>332</v>
-      </c>
-      <c r="N21" s="18"/>
-      <c r="O21" s="18"/>
-      <c r="P21" s="18"/>
-      <c r="Q21" s="18">
-        <v>1</v>
-      </c>
-      <c r="R21" s="18">
-        <v>201</v>
-      </c>
-      <c r="S21" s="18" t="s">
-        <v>293</v>
-      </c>
-      <c r="T21" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="U21" s="18" t="s">
-        <v>294</v>
-      </c>
-      <c r="V21" s="18">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22" ht="90" x14ac:dyDescent="0.25">
-      <c r="A22" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="B22" s="17" t="s">
-        <v>323</v>
-      </c>
-      <c r="C22" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="D22" s="17">
-        <v>28</v>
-      </c>
-      <c r="E22" s="17" t="s">
-        <v>330</v>
-      </c>
-      <c r="F22" s="17" t="s">
-        <v>331</v>
-      </c>
-      <c r="G22" s="17" t="s">
-        <v>326</v>
-      </c>
-      <c r="H22" s="17"/>
-      <c r="I22" s="19">
-        <v>98</v>
-      </c>
-      <c r="J22" s="17" t="s">
-        <v>332</v>
-      </c>
-      <c r="K22" s="19">
-        <v>98</v>
-      </c>
-      <c r="L22" s="17">
-        <v>98</v>
-      </c>
-      <c r="M22" s="17" t="s">
-        <v>332</v>
-      </c>
-      <c r="N22" s="17"/>
-      <c r="O22" s="17"/>
-      <c r="P22" s="17"/>
-      <c r="Q22" s="17">
-        <v>2</v>
-      </c>
-      <c r="R22" s="17">
-        <v>201</v>
-      </c>
-      <c r="S22" s="17" t="s">
-        <v>293</v>
-      </c>
-      <c r="T22" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="U22" s="17" t="s">
-        <v>294</v>
-      </c>
-      <c r="V22" s="17">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22" ht="90" x14ac:dyDescent="0.25">
-      <c r="A23" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="B23" s="18" t="s">
-        <v>323</v>
-      </c>
-      <c r="C23" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="D23" s="18">
-        <v>29</v>
-      </c>
-      <c r="E23" s="18" t="s">
-        <v>330</v>
-      </c>
-      <c r="F23" s="18" t="s">
-        <v>331</v>
-      </c>
-      <c r="G23" s="18" t="s">
-        <v>326</v>
-      </c>
-      <c r="H23" s="18"/>
-      <c r="I23" s="20">
-        <v>94</v>
-      </c>
-      <c r="J23" s="18" t="s">
-        <v>332</v>
-      </c>
-      <c r="K23" s="20">
-        <v>94</v>
-      </c>
-      <c r="L23" s="18">
-        <v>94</v>
-      </c>
-      <c r="M23" s="18" t="s">
-        <v>332</v>
-      </c>
-      <c r="N23" s="18"/>
-      <c r="O23" s="18"/>
-      <c r="P23" s="18"/>
-      <c r="Q23" s="18">
-        <v>3</v>
-      </c>
-      <c r="R23" s="18">
-        <v>201</v>
-      </c>
-      <c r="S23" s="18" t="s">
-        <v>293</v>
-      </c>
-      <c r="T23" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="U23" s="18" t="s">
-        <v>294</v>
-      </c>
-      <c r="V23" s="18">
-        <v>172</v>
-      </c>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="A2:V4">
-    <cfRule type="notContainsBlanks" dxfId="0" priority="1">
-      <formula>LEN(TRIM(A2))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.5703125" style="1" customWidth="1"/>
@@ -3909,30 +2006,6 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>334</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -3943,27 +2016,30 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BDDED82-7289-408A-8597-CE1381ED9DDD}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="27.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
-        <v>339</v>
-      </c>
-      <c r="B1" s="23" t="s">
-        <v>340</v>
-      </c>
-      <c r="C1" s="23" t="s">
-        <v>341</v>
-      </c>
-      <c r="D1" s="23" t="s">
-        <v>342</v>
-      </c>
-      <c r="E1" s="23" t="s">
-        <v>343</v>
-      </c>
-      <c r="F1" s="23" t="s">
-        <v>344</v>
+      <c r="A1" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -3974,10 +2050,132 @@
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>345</v>
-      </c>
-      <c r="D2">
+        <v>255</v>
+      </c>
+      <c r="D2" t="s">
+        <v>256</v>
+      </c>
+      <c r="E2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3">
         <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>255</v>
+      </c>
+      <c r="D3" t="s">
+        <v>256</v>
+      </c>
+      <c r="E3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" t="s">
+        <v>255</v>
+      </c>
+      <c r="D4" t="s">
+        <v>256</v>
+      </c>
+      <c r="E4" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>255</v>
+      </c>
+      <c r="D5" t="s">
+        <v>256</v>
+      </c>
+      <c r="E5" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
+        <v>255</v>
+      </c>
+      <c r="D6" t="s">
+        <v>256</v>
+      </c>
+      <c r="E6" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>255</v>
+      </c>
+      <c r="D7" t="s">
+        <v>256</v>
+      </c>
+      <c r="E7" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
+        <v>255</v>
+      </c>
+      <c r="D8" t="s">
+        <v>256</v>
+      </c>
+      <c r="E8" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>255</v>
+      </c>
+      <c r="D9" t="s">
+        <v>256</v>
+      </c>
+      <c r="E9" t="s">
+        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -3996,197 +2194,197 @@
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="F1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="O1" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="Q1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="U1" s="2" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="F2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="K2" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="L2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="M2" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="N2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="O2" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="P2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="Q2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="R2" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="S2" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="O2" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="P2" s="3" t="s">
+      <c r="T2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="U2" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="S2" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="U2" s="3" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
@@ -4256,46 +2454,46 @@
     </row>
     <row r="5" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D5" s="5">
         <v>1</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G5" s="5">
         <v>1</v>
       </c>
       <c r="H5" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="L5" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="M5" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="N5" s="5" t="s">
         <v>65</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>69</v>
       </c>
       <c r="O5" s="5"/>
       <c r="P5"/>
@@ -4303,53 +2501,53 @@
         <v>151</v>
       </c>
       <c r="R5" s="6" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="S5" s="6" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="T5"/>
       <c r="U5"/>
     </row>
     <row r="6" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D6" s="5">
         <v>2</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G6" s="5">
         <v>1</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N6" s="5"/>
       <c r="O6" s="5"/>
@@ -4358,49 +2556,49 @@
       <c r="R6"/>
       <c r="S6"/>
       <c r="T6" s="5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="U6" s="5"/>
     </row>
     <row r="7" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D7" s="4">
         <v>3</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G7" s="4">
         <v>1</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="N7" s="5"/>
       <c r="O7" s="5"/>
@@ -4408,58 +2606,58 @@
         <v>43</v>
       </c>
       <c r="R7" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="T7" s="4" t="s">
         <v>70</v>
-      </c>
-      <c r="S7" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="T7" s="4" t="s">
-        <v>74</v>
       </c>
       <c r="U7" s="4"/>
     </row>
     <row r="8" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D8" s="4">
         <v>4</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G8" s="4">
         <v>2</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="K8" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="L8" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="L8" s="5" t="s">
-        <v>82</v>
-      </c>
       <c r="M8" s="5" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="N8" s="5" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="O8" s="5"/>
       <c r="P8" s="4">
@@ -4490,170 +2688,170 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="K1" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="I1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="K1" s="12" t="s">
-        <v>297</v>
-      </c>
-      <c r="L1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="K2" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="L2" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="M2" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="I2" s="3" t="s">
+      <c r="N2" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>104</v>
-      </c>
       <c r="O2" s="3" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -4714,32 +2912,32 @@
     </row>
     <row r="5" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D5" s="5">
         <v>1</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="I5" s="5"/>
       <c r="J5" s="5" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
@@ -4748,38 +2946,38 @@
       </c>
       <c r="N5" s="5"/>
       <c r="Q5" s="5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="R5" s="5"/>
     </row>
     <row r="6" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D6" s="5">
         <v>1</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F6" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="G6" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>111</v>
-      </c>
       <c r="H6" s="5" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="I6" s="5"/>
       <c r="J6" s="5" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
@@ -4788,44 +2986,44 @@
       </c>
       <c r="N6" s="5"/>
       <c r="O6" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="R6" s="5"/>
     </row>
     <row r="7" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D7" s="7">
         <v>5</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F7" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="G7" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>111</v>
-      </c>
       <c r="H7" s="5" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="I7" s="5"/>
       <c r="J7" s="5" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="K7" s="5"/>
       <c r="L7" s="5"/>
@@ -4834,38 +3032,38 @@
       </c>
       <c r="N7" s="5"/>
       <c r="Q7" s="5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="R7" s="5"/>
     </row>
     <row r="8" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D8" s="7">
         <v>14</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F8" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="G8" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>111</v>
-      </c>
       <c r="H8" s="5" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="I8" s="5"/>
       <c r="J8" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="K8" s="5"/>
       <c r="L8" s="5"/>
@@ -4874,46 +3072,46 @@
       </c>
       <c r="N8" s="5"/>
       <c r="O8" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="Q8" s="5"/>
       <c r="R8" s="5"/>
     </row>
     <row r="9" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D9" s="4">
         <v>1</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F9" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>111</v>
-      </c>
       <c r="H9" s="5" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="I9" s="5"/>
       <c r="J9" s="5" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="K9" s="5"/>
       <c r="L9" s="5" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="M9" s="5">
         <v>4</v>
@@ -4926,32 +3124,32 @@
     </row>
     <row r="10" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D10" s="4">
         <v>2</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F10" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G10" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="G10" s="5" t="s">
-        <v>111</v>
-      </c>
       <c r="H10" s="5" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="I10" s="5"/>
       <c r="J10" s="5" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="K10" s="5"/>
       <c r="L10" s="5"/>
@@ -4960,42 +3158,42 @@
       </c>
       <c r="N10" s="5"/>
       <c r="Q10" s="5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="R10" s="5"/>
     </row>
     <row r="11" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D11" s="4">
         <v>3</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F11" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G11" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="G11" s="5" t="s">
-        <v>111</v>
-      </c>
       <c r="H11" s="5" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="I11" s="5"/>
       <c r="J11" s="5" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="K11" s="5"/>
       <c r="L11" s="5" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="M11" s="5">
         <v>48</v>
@@ -5008,34 +3206,34 @@
     </row>
     <row r="12" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D12" s="7">
         <v>4</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F12" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="G12" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="G12" s="5" t="s">
-        <v>111</v>
-      </c>
       <c r="H12" s="5" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="K12" s="5"/>
       <c r="L12" s="5"/>
@@ -5044,40 +3242,40 @@
       </c>
       <c r="N12" s="5"/>
       <c r="Q12" s="5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="R12" s="5"/>
     </row>
     <row r="13" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D13" s="7">
         <v>1</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="K13" s="5"/>
       <c r="L13" s="5"/>
@@ -5086,42 +3284,42 @@
       </c>
       <c r="N13" s="5"/>
       <c r="Q13" s="5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="R13" s="5"/>
     </row>
     <row r="14" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D14" s="7">
         <v>2</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F14" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="G14" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="G14" s="5" t="s">
-        <v>111</v>
-      </c>
       <c r="H14" s="5" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="I14" s="5"/>
       <c r="J14" s="5" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="K14" s="5"/>
       <c r="L14" s="5" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="M14" s="5">
         <v>37</v>
@@ -5134,36 +3332,36 @@
     </row>
     <row r="15" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D15" s="7">
         <v>4</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F15" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="G15" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="G15" s="5" t="s">
-        <v>111</v>
-      </c>
       <c r="H15" s="5" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="I15" s="5"/>
       <c r="J15" s="5" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="K15" s="5"/>
       <c r="L15" s="5" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="M15" s="5">
         <v>125</v>
@@ -5172,46 +3370,46 @@
         <v>181</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="Q15" s="5"/>
       <c r="R15" s="5"/>
     </row>
     <row r="16" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D16" s="7">
         <v>1</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="I16" s="5"/>
       <c r="J16" s="5" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="K16" s="5"/>
       <c r="L16" s="5" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="M16" s="5">
         <v>14</v>
@@ -5224,36 +3422,36 @@
     </row>
     <row r="17" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D17" s="7">
         <v>5</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="I17" s="5"/>
       <c r="J17" s="5" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="K17" s="5"/>
       <c r="L17" s="5" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M17" s="5">
         <v>100</v>
@@ -5266,36 +3464,36 @@
     </row>
     <row r="18" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D18" s="7">
         <v>8</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="I18" s="5"/>
       <c r="J18" s="5" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="K18" s="5"/>
       <c r="L18" s="5" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="M18" s="5">
         <v>42</v>
@@ -5324,225 +3522,225 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
-        <v>162</v>
+      <c r="A1" s="13" t="s">
+        <v>158</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E1" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="I1" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="Q1" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="R1" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="S1" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="T1" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="U1" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="R1" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="S1" s="5" t="s">
+      <c r="V1" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="W1" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="X1" s="2" t="s">
         <v>160</v>
-      </c>
-      <c r="U1" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="V1" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="W1" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="X1" s="2" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F2" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="J2" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="K2" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="L2" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="M2" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="N2" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="O2" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="P2" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="Q2" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="R2" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="S2" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="T2" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="U2" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="R2" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="S2" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="T2" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="U2" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="V2" s="14" t="s">
-        <v>296</v>
+      <c r="V2" s="10" t="s">
+        <v>244</v>
       </c>
       <c r="W2" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="X2" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="T3" s="5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="U3" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="V3" s="13" t="s">
-        <v>58</v>
+        <v>53</v>
+      </c>
+      <c r="V3" s="9" t="s">
+        <v>54</v>
       </c>
       <c r="W3" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="X3" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
@@ -5609,7 +3807,7 @@
       <c r="U4" s="5">
         <v>200</v>
       </c>
-      <c r="V4" s="13">
+      <c r="V4" s="9">
         <v>8</v>
       </c>
       <c r="W4" s="3">
@@ -5621,339 +3819,339 @@
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E5" s="5">
         <v>1</v>
       </c>
       <c r="F5" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="J5" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="K5" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="L5" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="M5" s="5" t="s">
         <v>186</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>190</v>
       </c>
       <c r="N5" s="5">
         <v>39</v>
       </c>
       <c r="O5" s="5" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="R5" s="5" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="S5" s="5" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="T5" s="5">
         <v>1</v>
       </c>
       <c r="U5" s="5" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="W5" s="5" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E6" s="5">
         <v>2</v>
       </c>
       <c r="F6" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="K6" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="L6" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="H6" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="L6" s="5" t="s">
-        <v>201</v>
-      </c>
       <c r="M6" s="5" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="N6" s="5">
         <v>93</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="P6" s="5">
         <v>35</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="S6" s="5" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="T6" s="5">
         <v>1</v>
       </c>
       <c r="U6" s="5" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="W6" s="5" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E7" s="5">
         <v>3</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="J7" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="M7" s="5" t="s">
         <v>199</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="L7" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="M7" s="5" t="s">
-        <v>203</v>
       </c>
       <c r="N7" s="5">
         <v>18</v>
       </c>
       <c r="O7" s="5" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="P7" s="5">
         <v>6</v>
       </c>
       <c r="R7" s="5" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="S7" s="5" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="T7" s="5">
         <v>1</v>
       </c>
       <c r="U7" s="5" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E8" s="5">
         <v>4</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="N8" s="5">
         <v>26</v>
       </c>
       <c r="O8" s="5" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="Q8" s="5">
         <v>36</v>
       </c>
       <c r="R8" s="5" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="S8" s="5" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="T8" s="5">
         <v>1</v>
       </c>
       <c r="U8" s="5" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="W8" s="5" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E9" s="5">
         <v>5</v>
       </c>
       <c r="F9" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="J9" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="K9" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="L9" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="I9" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="K9" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="L9" s="5" t="s">
-        <v>216</v>
-      </c>
       <c r="M9" s="5" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="N9" s="5">
         <v>0.03</v>
       </c>
       <c r="O9" s="5" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="P9" s="5">
         <v>0</v>
       </c>
       <c r="Q9" s="5" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="R9" s="5" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="S9" s="5" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="T9" s="5">
         <v>1</v>
       </c>
       <c r="U9" s="5" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:U4">
-    <cfRule type="notContainsBlanks" dxfId="7" priority="4">
+    <cfRule type="notContainsBlanks" dxfId="4" priority="4">
       <formula>LEN(TRIM(A2))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V4">
-    <cfRule type="notContainsBlanks" dxfId="6" priority="1">
+    <cfRule type="notContainsBlanks" dxfId="3" priority="1">
       <formula>LEN(TRIM(V2))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:X4">
-    <cfRule type="notContainsBlanks" dxfId="5" priority="3">
+    <cfRule type="notContainsBlanks" dxfId="2" priority="3">
       <formula>LEN(TRIM(W2))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5970,184 +4168,184 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="18" width="20.7109375" style="5" customWidth="1"/>
-    <col min="19" max="19" width="20.7109375" style="21" customWidth="1"/>
+    <col min="19" max="19" width="20.7109375" style="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="I1" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="J1" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="F1" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="G1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="M1" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="P1" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="J1" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="K1" s="5" t="s">
+      <c r="Q1" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="R1" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="S1" s="2" t="s">
         <v>227</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E2" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="M2" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="K2" s="5" t="s">
+      <c r="N2" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="L2" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>179</v>
-      </c>
       <c r="O2" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>296</v>
+        <v>244</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
@@ -6211,249 +4409,249 @@
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D5" s="5">
         <v>1</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="O5" s="5" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="P5" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="R5" s="5" t="s">
         <v>109</v>
-      </c>
-      <c r="R5" s="5" t="s">
-        <v>113</v>
       </c>
       <c r="S5" s="5"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D6" s="5">
         <v>2</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F6" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="H6" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>242</v>
-      </c>
       <c r="I6" s="5" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="S6" s="5"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D7" s="5">
         <v>3</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="G7" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="H7" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="H7" s="5" t="s">
-        <v>243</v>
-      </c>
       <c r="I7" s="5" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="O7" s="5" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="P7" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="R7" s="5" t="s">
         <v>109</v>
-      </c>
-      <c r="R7" s="5" t="s">
-        <v>113</v>
       </c>
       <c r="S7" s="5"/>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="M8" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="M8" s="5" t="s">
-        <v>241</v>
-      </c>
       <c r="O8" s="5" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="P8" s="5" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="S8" s="5"/>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="M9" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="L9" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="M9" s="5" t="s">
-        <v>241</v>
-      </c>
       <c r="O9" s="5" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="P9" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="R9" s="5" t="s">
         <v>109</v>
-      </c>
-      <c r="R9" s="5" t="s">
-        <v>113</v>
       </c>
       <c r="S9" s="5"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:J4 M2:S4">
-    <cfRule type="notContainsBlanks" dxfId="4" priority="5">
+    <cfRule type="notContainsBlanks" dxfId="1" priority="5">
       <formula>LEN(TRIM(A2))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:L4">
-    <cfRule type="notContainsBlanks" dxfId="3" priority="3">
+    <cfRule type="notContainsBlanks" dxfId="0" priority="3">
       <formula>LEN(TRIM(K2))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6464,687 +4662,24 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{803C895A-71FF-4E02-8999-07460F53FFBB}">
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" customWidth="1"/>
-    <col min="11" max="11" width="11.85546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>248</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>249</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>252</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="K1" s="15" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="60" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>256</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="K2" s="9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="9">
-        <v>12</v>
-      </c>
-      <c r="B4" s="9">
-        <v>2</v>
-      </c>
-      <c r="C4" s="9">
-        <v>8</v>
-      </c>
-      <c r="D4" s="9">
-        <v>7</v>
-      </c>
-      <c r="E4" s="9">
-        <v>26</v>
-      </c>
-      <c r="F4" s="9">
-        <v>9</v>
-      </c>
-      <c r="G4" s="9">
-        <v>10</v>
-      </c>
-      <c r="H4" s="9">
-        <v>10</v>
-      </c>
-      <c r="I4" s="9">
-        <v>8</v>
-      </c>
-      <c r="J4" s="9">
-        <v>8</v>
-      </c>
-      <c r="K4" s="9">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="I5" s="5">
-        <v>-7</v>
-      </c>
-      <c r="J5" s="5">
-        <v>1</v>
-      </c>
-      <c r="K5" s="5">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="A2:K4">
-    <cfRule type="notContainsBlanks" dxfId="2" priority="1">
-      <formula>LEN(TRIM(A2))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Comment xmlns="9dee18c2-6da5-44c1-913e-bf7f393fe0e8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCE85576-D13E-47AC-B7EE-857DE52A312D}">
-  <dimension ref="A1:K14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="11" width="20.7109375" style="5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>265</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="5">
-        <v>12</v>
-      </c>
-      <c r="B4" s="5">
-        <v>2</v>
-      </c>
-      <c r="C4" s="5">
-        <v>8</v>
-      </c>
-      <c r="D4" s="5">
-        <v>8</v>
-      </c>
-      <c r="E4" s="5">
-        <v>200</v>
-      </c>
-      <c r="F4" s="5">
-        <v>10</v>
-      </c>
-      <c r="G4" s="5">
-        <v>10</v>
-      </c>
-      <c r="H4" s="5">
-        <v>10</v>
-      </c>
-      <c r="I4" s="5">
-        <v>8</v>
-      </c>
-      <c r="J4" s="5">
-        <v>8</v>
-      </c>
-      <c r="K4" s="5">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D5" s="5">
-        <v>1</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="I5" s="5">
-        <v>-7</v>
-      </c>
-      <c r="J5" s="5">
-        <v>-7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D6" s="5">
-        <v>2</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="I6" s="5">
-        <v>-2</v>
-      </c>
-      <c r="J6" s="5">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D7" s="5">
-        <v>3</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="I7" s="5">
-        <v>1</v>
-      </c>
-      <c r="J7" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D8" s="5">
-        <v>4</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="I8" s="5">
-        <v>14</v>
-      </c>
-      <c r="J8" s="5">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D9" s="5">
-        <v>5</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="I9" s="5">
-        <v>27</v>
-      </c>
-      <c r="J9" s="5">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D10" s="5">
-        <v>5.01</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="I10" s="5">
-        <v>29</v>
-      </c>
-      <c r="J10" s="5">
-        <v>29</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D11" s="5">
-        <v>7</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="I11" s="5">
-        <v>42</v>
-      </c>
-      <c r="J11" s="5">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D12" s="5">
-        <v>8</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="I12" s="5">
-        <v>55</v>
-      </c>
-      <c r="J12" s="5">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D13" s="5">
-        <v>101</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="I13" s="5">
-        <v>77</v>
-      </c>
-      <c r="J13" s="5">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="45" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D14" s="5">
-        <v>201</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="I14" s="5">
-        <v>172</v>
-      </c>
-      <c r="J14" s="5">
-        <v>172</v>
-      </c>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="A2:H4 I2:L4">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="1">
-      <formula>LEN(TRIM(A2))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010090ADB40D834AE945B19FCDA4041AC0CB" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c09bae7b217a3930fedb3a6204001e96">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9dee18c2-6da5-44c1-913e-bf7f393fe0e8" xmlns:ns3="63ea592b-d684-45c7-8cdc-fad8f8e6bb41" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ac018b55a0c98af8ca0cc741473a0b1c" ns2:_="" ns3:_="">
     <xsd:import namespace="9dee18c2-6da5-44c1-913e-bf7f393fe0e8"/>
@@ -7367,24 +4902,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68D2B826-D4BB-4F95-9EB6-C2567A4D352D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9dee18c2-6da5-44c1-913e-bf7f393fe0e8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Comment xmlns="9dee18c2-6da5-44c1-913e-bf7f393fe0e8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3BEB11F-0E5C-4B66-89CC-AB3651412BF0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAA37260-A745-4F1A-87F7-7324275C4FF1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7401,22 +4937,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3BEB11F-0E5C-4B66-89CC-AB3651412BF0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68D2B826-D4BB-4F95-9EB6-C2567A4D352D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9dee18c2-6da5-44c1-913e-bf7f393fe0e8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/rules/CORE-000852/negative/01/data/unit-test-coreid-CG0330-negative.xlsx
+++ b/rules/CORE-000852/negative/01/data/unit-test-coreid-CG0330-negative.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10920"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\verisian\core-contributor\rules\CORE-000852\negative\01\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rich/Documents/github/core-contributor/rules/CORE-000852/negative/01/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B848F65-4212-448F-9DAA-966AF154808A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82D157FF-5971-4C42-9C13-BAA89141B28F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30330" yWindow="855" windowWidth="23265" windowHeight="14505" tabRatio="576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30340" yWindow="860" windowWidth="23260" windowHeight="14500" tabRatio="576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="30" r:id="rId1"/>
@@ -818,7 +818,7 @@
     <t>$column_order_from_dataset</t>
   </si>
   <si>
-    <t>$column_order_from_library</t>
+    <t>$library_with_dataset_only</t>
   </si>
 </sst>
 </file>
@@ -959,7 +959,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -990,13 +990,7 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1933,9 +1927,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D962C8A-AFA1-4EE3-9E57-8981969F2E6E}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>10</v>
       </c>
@@ -1943,7 +1937,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1959,14 +1953,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="36.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.7109375" customWidth="1"/>
+    <col min="1" max="1" width="11.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="36.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1974,7 +1968,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1982,7 +1976,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1990,7 +1984,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -1998,7 +1992,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -2017,12 +2011,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BDDED82-7289-408A-8597-CE1381ED9DDD}">
   <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="5" max="5" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="11" t="s">
         <v>249</v>
       </c>
@@ -2042,7 +2036,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2059,7 +2053,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2076,7 +2070,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2093,7 +2087,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>2</v>
       </c>
@@ -2110,7 +2104,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>3</v>
       </c>
@@ -2127,7 +2121,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>3</v>
       </c>
@@ -2144,7 +2138,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>4</v>
       </c>
@@ -2161,7 +2155,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>4</v>
       </c>
@@ -2180,23 +2174,24 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:U8"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="21" width="20.7109375" style="2" customWidth="1"/>
-    <col min="22" max="16384" width="8.85546875" style="2"/>
+    <col min="1" max="21" width="20.6640625" style="2" customWidth="1"/>
+    <col min="22" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -2257,7 +2252,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>33</v>
       </c>
@@ -2322,7 +2317,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>53</v>
       </c>
@@ -2387,7 +2382,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>50</v>
       </c>
@@ -2452,7 +2447,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>55</v>
       </c>
@@ -2509,7 +2504,7 @@
       <c r="T5"/>
       <c r="U5"/>
     </row>
-    <row r="6" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>55</v>
       </c>
@@ -2560,7 +2555,7 @@
       </c>
       <c r="U6" s="5"/>
     </row>
-    <row r="7" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>55</v>
       </c>
@@ -2616,7 +2611,7 @@
       </c>
       <c r="U7" s="4"/>
     </row>
-    <row r="8" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" ht="32" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>55</v>
       </c>
@@ -2680,13 +2675,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B41BDCC7-F382-49D0-BD18-4F06A3554CB3}">
   <dimension ref="A1:R18"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="18" width="20.7109375" style="2" customWidth="1"/>
-    <col min="19" max="16384" width="8.85546875" style="2"/>
+    <col min="1" max="18" width="20.6640625" style="2" customWidth="1"/>
+    <col min="19" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>14</v>
       </c>
@@ -2717,7 +2712,7 @@
       <c r="J1" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="2" t="s">
         <v>245</v>
       </c>
       <c r="L1" s="2" t="s">
@@ -2742,7 +2737,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>33</v>
       </c>
@@ -2798,7 +2793,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>53</v>
       </c>
@@ -2854,7 +2849,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>50</v>
       </c>
@@ -2910,7 +2905,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>55</v>
       </c>
@@ -2950,7 +2945,7 @@
       </c>
       <c r="R5" s="5"/>
     </row>
-    <row r="6" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>55</v>
       </c>
@@ -2996,7 +2991,7 @@
       </c>
       <c r="R6" s="5"/>
     </row>
-    <row r="7" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
         <v>55</v>
       </c>
@@ -3036,7 +3031,7 @@
       </c>
       <c r="R7" s="5"/>
     </row>
-    <row r="8" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
         <v>55</v>
       </c>
@@ -3080,7 +3075,7 @@
       <c r="Q8" s="5"/>
       <c r="R8" s="5"/>
     </row>
-    <row r="9" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>55</v>
       </c>
@@ -3122,7 +3117,7 @@
       <c r="Q9" s="5"/>
       <c r="R9" s="5"/>
     </row>
-    <row r="10" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>55</v>
       </c>
@@ -3162,7 +3157,7 @@
       </c>
       <c r="R10" s="5"/>
     </row>
-    <row r="11" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>55</v>
       </c>
@@ -3204,7 +3199,7 @@
       <c r="Q11" s="5"/>
       <c r="R11" s="5"/>
     </row>
-    <row r="12" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
         <v>55</v>
       </c>
@@ -3246,7 +3241,7 @@
       </c>
       <c r="R12" s="5"/>
     </row>
-    <row r="13" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
         <v>55</v>
       </c>
@@ -3288,7 +3283,7 @@
       </c>
       <c r="R13" s="5"/>
     </row>
-    <row r="14" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
         <v>55</v>
       </c>
@@ -3330,7 +3325,7 @@
       <c r="Q14" s="5"/>
       <c r="R14" s="5"/>
     </row>
-    <row r="15" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
         <v>55</v>
       </c>
@@ -3378,7 +3373,7 @@
       <c r="Q15" s="5"/>
       <c r="R15" s="5"/>
     </row>
-    <row r="16" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
         <v>55</v>
       </c>
@@ -3420,7 +3415,7 @@
       <c r="Q16" s="5"/>
       <c r="R16" s="5"/>
     </row>
-    <row r="17" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="7" t="s">
         <v>55</v>
       </c>
@@ -3462,7 +3457,7 @@
       <c r="Q17" s="5"/>
       <c r="R17" s="5"/>
     </row>
-    <row r="18" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="7" t="s">
         <v>55</v>
       </c>
@@ -3516,13 +3511,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E928109-8D06-4717-9DE5-10A023DB72D3}">
   <dimension ref="A1:X9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="24" width="20.7109375" style="5" customWidth="1"/>
+    <col min="1" max="24" width="20.6640625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:24" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" s="12" t="s">
         <v>158</v>
       </c>
       <c r="B1" s="5" t="s">
@@ -3595,7 +3590,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="2" spans="1:24" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" ht="48" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>177</v>
       </c>
@@ -3669,7 +3664,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>53</v>
       </c>
@@ -3743,7 +3738,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4" s="5">
         <v>19</v>
       </c>
@@ -3817,7 +3812,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>191</v>
       </c>
@@ -3879,7 +3874,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>198</v>
       </c>
@@ -3947,7 +3942,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>201</v>
       </c>
@@ -4009,7 +4004,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>205</v>
       </c>
@@ -4074,7 +4069,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>214</v>
       </c>
@@ -4165,13 +4160,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F69B0C80-0D21-48CC-B786-5AC734E98D04}">
   <dimension ref="A1:S9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="18" width="20.7109375" style="5" customWidth="1"/>
-    <col min="19" max="19" width="20.7109375" style="6" customWidth="1"/>
+    <col min="1" max="18" width="20.6640625" style="5" customWidth="1"/>
+    <col min="19" max="19" width="20.6640625" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>14</v>
       </c>
@@ -4196,7 +4191,7 @@
       <c r="H1" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="5" t="s">
         <v>221</v>
       </c>
       <c r="J1" s="5" t="s">
@@ -4230,7 +4225,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="48" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>33</v>
       </c>
@@ -4289,7 +4284,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>53</v>
       </c>
@@ -4348,7 +4343,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="5">
         <v>12</v>
       </c>
@@ -4407,7 +4402,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>55</v>
       </c>
@@ -4458,7 +4453,7 @@
       </c>
       <c r="S5" s="5"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>55</v>
       </c>
@@ -4506,7 +4501,7 @@
       </c>
       <c r="S6" s="5"/>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>55</v>
       </c>
@@ -4551,7 +4546,7 @@
       </c>
       <c r="S7" s="5"/>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>55</v>
       </c>
@@ -4596,7 +4591,7 @@
       </c>
       <c r="S8" s="5"/>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>55</v>
       </c>
@@ -4671,15 +4666,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010090ADB40D834AE945B19FCDA4041AC0CB" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c09bae7b217a3930fedb3a6204001e96">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9dee18c2-6da5-44c1-913e-bf7f393fe0e8" xmlns:ns3="63ea592b-d684-45c7-8cdc-fad8f8e6bb41" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ac018b55a0c98af8ca0cc741473a0b1c" ns2:_="" ns3:_="">
     <xsd:import namespace="9dee18c2-6da5-44c1-913e-bf7f393fe0e8"/>
@@ -4902,6 +4888,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68D2B826-D4BB-4F95-9EB6-C2567A4D352D}">
   <ds:schemaRefs>
@@ -4913,14 +4908,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3BEB11F-0E5C-4B66-89CC-AB3651412BF0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAA37260-A745-4F1A-87F7-7324275C4FF1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4937,4 +4924,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3BEB11F-0E5C-4B66-89CC-AB3651412BF0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>